--- a/output/AAPL_ev_sales_model.xlsx
+++ b/output/AAPL_ev_sales_model.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,151 +442,227 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Model Inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Revenue (TTM):</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>391035000000</v>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>EV/Sales Multiple</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Target EV</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Target Equity Value</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Target Price</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Upside/Downside</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt:</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>76686000000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Conservative</t>
+          <t>Shares Outstanding:</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-76686000000</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-5.134375246085518</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-1.024315093986008</v>
+        <v>14935799649.32752</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Current Price:</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>211.16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Valuation Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>EV/Sales Multiple</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Target EV</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Target Equity Value</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Target Price</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Upside/Downside</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <f>$B$4*B11</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>C11-$B$5</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>D11/$B$6</f>
+        <v/>
+      </c>
+      <c r="F11" s="3">
+        <f>(E11-$B$7)/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Market Average</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B12" t="n">
         <v>3.5</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-76686000000</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-5.134375246085518</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>-1.024315093986008</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="C12">
+        <f>$B$4*B12</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>C12-$B$5</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>D12/$B$6</f>
+        <v/>
+      </c>
+      <c r="F12" s="3">
+        <f>(E12-$B$7)/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B13" t="n">
         <v>5</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-76686000000</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-5.134375246085518</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>-1.024315093986008</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="C13">
+        <f>$B$4*B13</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>C13-$B$5</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>D13/$B$6</f>
+        <v/>
+      </c>
+      <c r="F13" s="3">
+        <f>(E13-$B$7)/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Current Multiple</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B14" t="n">
         <v>7.778</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-76686000000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-5.134375246085518</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-1.024315093986008</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="C14">
+        <f>$B$4*B14</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>C14-$B$5</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>D14/$B$6</f>
+        <v/>
+      </c>
+      <c r="F14" s="3">
+        <f>(E14-$B$7)/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Target Multiple</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B15" t="n">
         <v>4.2</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-76686000000</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-5.134375246085518</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>-1.024315093986008</v>
+      <c r="C15">
+        <f>$B$4*B15</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>C15-$B$5</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>D15/$B$6</f>
+        <v/>
+      </c>
+      <c r="F15" s="3">
+        <f>(E15-$B$7)/$B$7</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/AAPL_ev_sales_model.xlsx
+++ b/output/AAPL_ev_sales_model.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,177 +492,220 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Valuation Analysis</t>
+          <t>Growth Assumptions</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Revenue Growth Rate (Annual):</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>5-Year Exit Valuation Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>EV/Sales Multiple</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Target EV</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Target Equity Value</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Target Price</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Upside/Downside</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <f>$B$4*B11</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>C11-$B$5</f>
-        <v/>
-      </c>
-      <c r="E11">
-        <f>D11/$B$6</f>
-        <v/>
-      </c>
-      <c r="F11" s="3">
-        <f>(E11-$B$7)/$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Market Average</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C12">
-        <f>$B$4*B12</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>C12-$B$5</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>D12/$B$6</f>
-        <v/>
-      </c>
-      <c r="F12" s="3">
-        <f>(E12-$B$7)/$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13">
-        <f>$B$4*B13</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>C13-$B$5</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>D13/$B$6</f>
-        <v/>
-      </c>
-      <c r="F13" s="3">
-        <f>(E13-$B$7)/$B$7</f>
-        <v/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Exit Multiple</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Year 5 Revenue</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Exit EV</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Exit Equity Value</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Exit Price</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Total Return</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Current Multiple</t>
+          <t>Conservative</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.778</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <f>$B$4*B14</f>
+        <f>$B$4*(1+$B$10)^5</f>
         <v/>
       </c>
       <c r="D14">
-        <f>C14-$B$5</f>
+        <f>C14*B14</f>
         <v/>
       </c>
       <c r="E14">
-        <f>D14/$B$6</f>
-        <v/>
-      </c>
-      <c r="F14" s="3">
-        <f>(E14-$B$7)/$B$7</f>
+        <f>D14-$B$5</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>E14/$B$6</f>
+        <v/>
+      </c>
+      <c r="G14" s="3">
+        <f>(F14/$B$7)^(1/5)-1</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Market Average</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C15">
+        <f>$B$4*(1+$B$10)^5</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>C15*B15</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>D15-$B$5</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>E15/$B$6</f>
+        <v/>
+      </c>
+      <c r="G15" s="3">
+        <f>(F15/$B$7)^(1/5)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <f>$B$4*(1+$B$10)^5</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>C16*B16</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>D16-$B$5</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>E16/$B$6</f>
+        <v/>
+      </c>
+      <c r="G16" s="3">
+        <f>(F16/$B$7)^(1/5)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Current Multiple</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7.778</v>
+      </c>
+      <c r="C17">
+        <f>$B$4*(1+$B$10)^5</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>C17*B17</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>D17-$B$5</f>
+        <v/>
+      </c>
+      <c r="F17">
+        <f>E17/$B$6</f>
+        <v/>
+      </c>
+      <c r="G17" s="3">
+        <f>(F17/$B$7)^(1/5)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Target Multiple</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B18" t="n">
         <v>4.2</v>
       </c>
-      <c r="C15">
-        <f>$B$4*B15</f>
-        <v/>
-      </c>
-      <c r="D15">
-        <f>C15-$B$5</f>
-        <v/>
-      </c>
-      <c r="E15">
-        <f>D15/$B$6</f>
-        <v/>
-      </c>
-      <c r="F15" s="3">
-        <f>(E15-$B$7)/$B$7</f>
+      <c r="C18">
+        <f>$B$4*(1+$B$10)^5</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>C18*B18</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>D18-$B$5</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>E18/$B$6</f>
+        <v/>
+      </c>
+      <c r="G18" s="3">
+        <f>(F18/$B$7)^(1/5)-1</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A12:G12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/AAPL_ev_sales_model.xlsx
+++ b/output/AAPL_ev_sales_model.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,10 +33,19 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,12 +54,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00366092"/>
         <bgColor rgb="00366092"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -58,14 +73,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick"/>
+      <right style="thick"/>
+      <top style="thick"/>
+      <bottom style="thick"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -438,12 +461,39 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AAPL - EV/Sales Valuation Model</t>
+          <t>EV/Sales Valuation Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ticker Symbol:</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>To analyze a new symbol:</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>1. Change symbol in B2</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2. Run: python examples/analyze_stock.py [NEW_SYMBOL]</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Model Inputs</t>
         </is>
@@ -490,7 +540,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Growth Assumptions</t>
         </is>
@@ -502,49 +552,49 @@
           <t>Revenue Growth Rate (Annual):</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="5" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>5-Year Exit Valuation Analysis</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Exit Multiple</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Year 5 Revenue</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Exit EV</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Exit Equity Value</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Total Return</t>
         </is>
@@ -575,7 +625,7 @@
         <f>E14/$B$6</f>
         <v/>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="5">
         <f>(F14/$B$7)^(1/5)-1</f>
         <v/>
       </c>
@@ -605,7 +655,7 @@
         <f>E15/$B$6</f>
         <v/>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="5">
         <f>(F15/$B$7)^(1/5)-1</f>
         <v/>
       </c>
@@ -635,7 +685,7 @@
         <f>E16/$B$6</f>
         <v/>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="5">
         <f>(F16/$B$7)^(1/5)-1</f>
         <v/>
       </c>
@@ -665,7 +715,7 @@
         <f>E17/$B$6</f>
         <v/>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="5">
         <f>(F17/$B$7)^(1/5)-1</f>
         <v/>
       </c>
@@ -695,7 +745,7 @@
         <f>E18/$B$6</f>
         <v/>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="5">
         <f>(F18/$B$7)^(1/5)-1</f>
         <v/>
       </c>
